--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_07-10-2025.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_07-10-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -518,17 +518,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£10.30</t>
+          <t>£10.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.30</t>
+          <t>£10.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.30</t>
+          <t>£10.00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.mgnbm.co.uk/25mm-pir-insulation-board-2400mm-x-1200mm-8-x-4/</t>
+          <t>£14.54</t>
         </is>
       </c>
     </row>
@@ -595,17 +595,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£11.60</t>
+          <t>£11.30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.60</t>
+          <t>£11.30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£11.60</t>
+          <t>£11.30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -636,27 +636,27 @@
       <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6cdd21eb5+80197]
-	GetHandleVerifier [0x0x7ff6cdd21f10+80288]
-	(No symbol) [0x0x7ff6cdaa02fa]
-	(No symbol) [0x0x7ff6cdaf7cd7]
-	(No symbol) [0x0x7ff6cdaf7f9c]
-	(No symbol) [0x0x7ff6cdb4ba87]
-	(No symbol) [0x0x7ff6cdb203bf]
-	(No symbol) [0x0x7ff6cdb487fb]
-	(No symbol) [0x0x7ff6cdb20153]
-	(No symbol) [0x0x7ff6cdae8b02]
-	(No symbol) [0x0x7ff6cdae98d3]
-	GetHandleVerifier [0x0x7ff6cdfde83d+2949837]
-	GetHandleVerifier [0x0x7ff6cdfd8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6cdff86c7+3055959]
-	GetHandleVerifier [0x0x7ff6cdd3cfee+191102]
-	GetHandleVerifier [0x0x7ff6cdd450af+224063]
-	GetHandleVerifier [0x0x7ff6cdd2af64+117236]
-	GetHandleVerifier [0x0x7ff6cdd2b119+117673]
-	GetHandleVerifier [0x0x7ff6cdd110a8+11064]
+	GetHandleVerifier [0x0x7ff7bf181eb5+80197]
+	GetHandleVerifier [0x0x7ff7bf181f10+80288]
+	(No symbol) [0x0x7ff7bef002fa]
+	(No symbol) [0x0x7ff7bef57cd7]
+	(No symbol) [0x0x7ff7bef57f9c]
+	(No symbol) [0x0x7ff7befaba87]
+	(No symbol) [0x0x7ff7bef803bf]
+	(No symbol) [0x0x7ff7befa87fb]
+	(No symbol) [0x0x7ff7bef80153]
+	(No symbol) [0x0x7ff7bef48b02]
+	(No symbol) [0x0x7ff7bef498d3]
+	GetHandleVerifier [0x0x7ff7bf43e83d+2949837]
+	GetHandleVerifier [0x0x7ff7bf438c6a+2926330]
+	GetHandleVerifier [0x0x7ff7bf4586c7+3055959]
+	GetHandleVerifier [0x0x7ff7bf19cfee+191102]
+	GetHandleVerifier [0x0x7ff7bf1a50af+224063]
+	GetHandleVerifier [0x0x7ff7bf18af64+117236]
+	GetHandleVerifier [0x0x7ff7bf18b119+117673]
+	GetHandleVerifier [0x0x7ff7bf1710a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -679,7 +679,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.mgnbm.co.uk/30mm-pir-insulation-board-2400mm-x-1200mm-8-x-4/</t>
+          <t>£19.36</t>
         </is>
       </c>
     </row>
@@ -696,17 +696,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£15.05</t>
+          <t>£14.60</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£15.05</t>
+          <t>£14.60</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£15.05</t>
+          <t>£14.60</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -737,27 +737,27 @@
       <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6cdd21eb5+80197]
-	GetHandleVerifier [0x0x7ff6cdd21f10+80288]
-	(No symbol) [0x0x7ff6cdaa02fa]
-	(No symbol) [0x0x7ff6cdaf7cd7]
-	(No symbol) [0x0x7ff6cdaf7f9c]
-	(No symbol) [0x0x7ff6cdb4ba87]
-	(No symbol) [0x0x7ff6cdb203bf]
-	(No symbol) [0x0x7ff6cdb487fb]
-	(No symbol) [0x0x7ff6cdb20153]
-	(No symbol) [0x0x7ff6cdae8b02]
-	(No symbol) [0x0x7ff6cdae98d3]
-	GetHandleVerifier [0x0x7ff6cdfde83d+2949837]
-	GetHandleVerifier [0x0x7ff6cdfd8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6cdff86c7+3055959]
-	GetHandleVerifier [0x0x7ff6cdd3cfee+191102]
-	GetHandleVerifier [0x0x7ff6cdd450af+224063]
-	GetHandleVerifier [0x0x7ff6cdd2af64+117236]
-	GetHandleVerifier [0x0x7ff6cdd2b119+117673]
-	GetHandleVerifier [0x0x7ff6cdd110a8+11064]
+	GetHandleVerifier [0x0x7ff7bf181eb5+80197]
+	GetHandleVerifier [0x0x7ff7bf181f10+80288]
+	(No symbol) [0x0x7ff7bef002fa]
+	(No symbol) [0x0x7ff7bef57cd7]
+	(No symbol) [0x0x7ff7bef57f9c]
+	(No symbol) [0x0x7ff7befaba87]
+	(No symbol) [0x0x7ff7bef803bf]
+	(No symbol) [0x0x7ff7befa87fb]
+	(No symbol) [0x0x7ff7bef80153]
+	(No symbol) [0x0x7ff7bef48b02]
+	(No symbol) [0x0x7ff7bef498d3]
+	GetHandleVerifier [0x0x7ff7bf43e83d+2949837]
+	GetHandleVerifier [0x0x7ff7bf438c6a+2926330]
+	GetHandleVerifier [0x0x7ff7bf4586c7+3055959]
+	GetHandleVerifier [0x0x7ff7bf19cfee+191102]
+	GetHandleVerifier [0x0x7ff7bf1a50af+224063]
+	GetHandleVerifier [0x0x7ff7bf18af64+117236]
+	GetHandleVerifier [0x0x7ff7bf18b119+117673]
+	GetHandleVerifier [0x0x7ff7bf1710a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.mgnbm.co.uk/40mm-pir-insulation-board-2400mm-x-1200mm-8-x-4/</t>
+          <t>£23.52</t>
         </is>
       </c>
     </row>
@@ -797,17 +797,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£15.35</t>
+          <t>£14.92</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£15.35</t>
+          <t>£14.92</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£15.35</t>
+          <t>£14.92</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -838,27 +838,27 @@
       <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6cdd21eb5+80197]
-	GetHandleVerifier [0x0x7ff6cdd21f10+80288]
-	(No symbol) [0x0x7ff6cdaa02fa]
-	(No symbol) [0x0x7ff6cdaf7cd7]
-	(No symbol) [0x0x7ff6cdaf7f9c]
-	(No symbol) [0x0x7ff6cdb4ba87]
-	(No symbol) [0x0x7ff6cdb203bf]
-	(No symbol) [0x0x7ff6cdb487fb]
-	(No symbol) [0x0x7ff6cdb20153]
-	(No symbol) [0x0x7ff6cdae8b02]
-	(No symbol) [0x0x7ff6cdae98d3]
-	GetHandleVerifier [0x0x7ff6cdfde83d+2949837]
-	GetHandleVerifier [0x0x7ff6cdfd8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6cdff86c7+3055959]
-	GetHandleVerifier [0x0x7ff6cdd3cfee+191102]
-	GetHandleVerifier [0x0x7ff6cdd450af+224063]
-	GetHandleVerifier [0x0x7ff6cdd2af64+117236]
-	GetHandleVerifier [0x0x7ff6cdd2b119+117673]
-	GetHandleVerifier [0x0x7ff6cdd110a8+11064]
+	GetHandleVerifier [0x0x7ff7bf181eb5+80197]
+	GetHandleVerifier [0x0x7ff7bf181f10+80288]
+	(No symbol) [0x0x7ff7bef002fa]
+	(No symbol) [0x0x7ff7bef57cd7]
+	(No symbol) [0x0x7ff7bef57f9c]
+	(No symbol) [0x0x7ff7befaba87]
+	(No symbol) [0x0x7ff7bef803bf]
+	(No symbol) [0x0x7ff7befa87fb]
+	(No symbol) [0x0x7ff7bef80153]
+	(No symbol) [0x0x7ff7bef48b02]
+	(No symbol) [0x0x7ff7bef498d3]
+	GetHandleVerifier [0x0x7ff7bf43e83d+2949837]
+	GetHandleVerifier [0x0x7ff7bf438c6a+2926330]
+	GetHandleVerifier [0x0x7ff7bf4586c7+3055959]
+	GetHandleVerifier [0x0x7ff7bf19cfee+191102]
+	GetHandleVerifier [0x0x7ff7bf1a50af+224063]
+	GetHandleVerifier [0x0x7ff7bf18af64+117236]
+	GetHandleVerifier [0x0x7ff7bf18b119+117673]
+	GetHandleVerifier [0x0x7ff7bf1710a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -881,7 +881,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.mgnbm.co.uk/50mm-pir-insulation-board-2400mm-x-1200mm-8-x-4/</t>
+          <t>£21.50</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£19.52</t>
+          <t>£18.99</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£19.52</t>
+          <t>£18.99</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£19.52</t>
+          <t>£18.99</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -939,27 +939,27 @@
       <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6cdd21eb5+80197]
-	GetHandleVerifier [0x0x7ff6cdd21f10+80288]
-	(No symbol) [0x0x7ff6cdaa02fa]
-	(No symbol) [0x0x7ff6cdaf7cd7]
-	(No symbol) [0x0x7ff6cdaf7f9c]
-	(No symbol) [0x0x7ff6cdb4ba87]
-	(No symbol) [0x0x7ff6cdb203bf]
-	(No symbol) [0x0x7ff6cdb487fb]
-	(No symbol) [0x0x7ff6cdb20153]
-	(No symbol) [0x0x7ff6cdae8b02]
-	(No symbol) [0x0x7ff6cdae98d3]
-	GetHandleVerifier [0x0x7ff6cdfde83d+2949837]
-	GetHandleVerifier [0x0x7ff6cdfd8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6cdff86c7+3055959]
-	GetHandleVerifier [0x0x7ff6cdd3cfee+191102]
-	GetHandleVerifier [0x0x7ff6cdd450af+224063]
-	GetHandleVerifier [0x0x7ff6cdd2af64+117236]
-	GetHandleVerifier [0x0x7ff6cdd2b119+117673]
-	GetHandleVerifier [0x0x7ff6cdd110a8+11064]
+	GetHandleVerifier [0x0x7ff7bf181eb5+80197]
+	GetHandleVerifier [0x0x7ff7bf181f10+80288]
+	(No symbol) [0x0x7ff7bef002fa]
+	(No symbol) [0x0x7ff7bef57cd7]
+	(No symbol) [0x0x7ff7bef57f9c]
+	(No symbol) [0x0x7ff7befaba87]
+	(No symbol) [0x0x7ff7bef803bf]
+	(No symbol) [0x0x7ff7befa87fb]
+	(No symbol) [0x0x7ff7bef80153]
+	(No symbol) [0x0x7ff7bef48b02]
+	(No symbol) [0x0x7ff7bef498d3]
+	GetHandleVerifier [0x0x7ff7bf43e83d+2949837]
+	GetHandleVerifier [0x0x7ff7bf438c6a+2926330]
+	GetHandleVerifier [0x0x7ff7bf4586c7+3055959]
+	GetHandleVerifier [0x0x7ff7bf19cfee+191102]
+	GetHandleVerifier [0x0x7ff7bf1a50af+224063]
+	GetHandleVerifier [0x0x7ff7bf18af64+117236]
+	GetHandleVerifier [0x0x7ff7bf18b119+117673]
+	GetHandleVerifier [0x0x7ff7bf1710a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -982,7 +982,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.mgnbm.co.uk/60mm-pir-insulation-board-2400mm-x-1200mm-8-x-4/</t>
+          <t>£33.40</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£21.30</t>
+          <t>£20.70</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£21.30</t>
+          <t>£20.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£21.30</t>
+          <t>£20.70</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1040,27 +1040,27 @@
       <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6cdd21eb5+80197]
-	GetHandleVerifier [0x0x7ff6cdd21f10+80288]
-	(No symbol) [0x0x7ff6cdaa02fa]
-	(No symbol) [0x0x7ff6cdaf7cd7]
-	(No symbol) [0x0x7ff6cdaf7f9c]
-	(No symbol) [0x0x7ff6cdb4ba87]
-	(No symbol) [0x0x7ff6cdb203bf]
-	(No symbol) [0x0x7ff6cdb487fb]
-	(No symbol) [0x0x7ff6cdb20153]
-	(No symbol) [0x0x7ff6cdae8b02]
-	(No symbol) [0x0x7ff6cdae98d3]
-	GetHandleVerifier [0x0x7ff6cdfde83d+2949837]
-	GetHandleVerifier [0x0x7ff6cdfd8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6cdff86c7+3055959]
-	GetHandleVerifier [0x0x7ff6cdd3cfee+191102]
-	GetHandleVerifier [0x0x7ff6cdd450af+224063]
-	GetHandleVerifier [0x0x7ff6cdd2af64+117236]
-	GetHandleVerifier [0x0x7ff6cdd2b119+117673]
-	GetHandleVerifier [0x0x7ff6cdd110a8+11064]
+	GetHandleVerifier [0x0x7ff7bf181eb5+80197]
+	GetHandleVerifier [0x0x7ff7bf181f10+80288]
+	(No symbol) [0x0x7ff7bef002fa]
+	(No symbol) [0x0x7ff7bef57cd7]
+	(No symbol) [0x0x7ff7bef57f9c]
+	(No symbol) [0x0x7ff7befaba87]
+	(No symbol) [0x0x7ff7bef803bf]
+	(No symbol) [0x0x7ff7befa87fb]
+	(No symbol) [0x0x7ff7bef80153]
+	(No symbol) [0x0x7ff7bef48b02]
+	(No symbol) [0x0x7ff7bef498d3]
+	GetHandleVerifier [0x0x7ff7bf43e83d+2949837]
+	GetHandleVerifier [0x0x7ff7bf438c6a+2926330]
+	GetHandleVerifier [0x0x7ff7bf4586c7+3055959]
+	GetHandleVerifier [0x0x7ff7bf19cfee+191102]
+	GetHandleVerifier [0x0x7ff7bf1a50af+224063]
+	GetHandleVerifier [0x0x7ff7bf18af64+117236]
+	GetHandleVerifier [0x0x7ff7bf18b119+117673]
+	GetHandleVerifier [0x0x7ff7bf1710a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.mgnbm.co.uk/70mm-pir-insulation-board-2400mm-x-1200mm-8-x-4/</t>
+          <t>£30.35</t>
         </is>
       </c>
     </row>
@@ -1100,17 +1100,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£21.53</t>
+          <t>£20.90</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£21.53</t>
+          <t>£20.90</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£21.53</t>
+          <t>£20.90</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1141,27 +1141,27 @@
       <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6cdd21eb5+80197]
-	GetHandleVerifier [0x0x7ff6cdd21f10+80288]
-	(No symbol) [0x0x7ff6cdaa02fa]
-	(No symbol) [0x0x7ff6cdaf7cd7]
-	(No symbol) [0x0x7ff6cdaf7f9c]
-	(No symbol) [0x0x7ff6cdb4ba87]
-	(No symbol) [0x0x7ff6cdb203bf]
-	(No symbol) [0x0x7ff6cdb487fb]
-	(No symbol) [0x0x7ff6cdb20153]
-	(No symbol) [0x0x7ff6cdae8b02]
-	(No symbol) [0x0x7ff6cdae98d3]
-	GetHandleVerifier [0x0x7ff6cdfde83d+2949837]
-	GetHandleVerifier [0x0x7ff6cdfd8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6cdff86c7+3055959]
-	GetHandleVerifier [0x0x7ff6cdd3cfee+191102]
-	GetHandleVerifier [0x0x7ff6cdd450af+224063]
-	GetHandleVerifier [0x0x7ff6cdd2af64+117236]
-	GetHandleVerifier [0x0x7ff6cdd2b119+117673]
-	GetHandleVerifier [0x0x7ff6cdd110a8+11064]
+	GetHandleVerifier [0x0x7ff7bf181eb5+80197]
+	GetHandleVerifier [0x0x7ff7bf181f10+80288]
+	(No symbol) [0x0x7ff7bef002fa]
+	(No symbol) [0x0x7ff7bef57cd7]
+	(No symbol) [0x0x7ff7bef57f9c]
+	(No symbol) [0x0x7ff7befaba87]
+	(No symbol) [0x0x7ff7bef803bf]
+	(No symbol) [0x0x7ff7befa87fb]
+	(No symbol) [0x0x7ff7bef80153]
+	(No symbol) [0x0x7ff7bef48b02]
+	(No symbol) [0x0x7ff7bef498d3]
+	GetHandleVerifier [0x0x7ff7bf43e83d+2949837]
+	GetHandleVerifier [0x0x7ff7bf438c6a+2926330]
+	GetHandleVerifier [0x0x7ff7bf4586c7+3055959]
+	GetHandleVerifier [0x0x7ff7bf19cfee+191102]
+	GetHandleVerifier [0x0x7ff7bf1a50af+224063]
+	GetHandleVerifier [0x0x7ff7bf18af64+117236]
+	GetHandleVerifier [0x0x7ff7bf18b119+117673]
+	GetHandleVerifier [0x0x7ff7bf1710a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.mgnbm.co.uk/75mm-pir-insulation-board-2400mm-x-1200mm-8-x-4/</t>
+          <t>£29.93</t>
         </is>
       </c>
     </row>
@@ -1201,17 +1201,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£24.75</t>
+          <t>£23.99</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£24.75</t>
+          <t>£23.99</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£24.75</t>
+          <t>£23.99</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1242,27 +1242,27 @@
       <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6cdd21eb5+80197]
-	GetHandleVerifier [0x0x7ff6cdd21f10+80288]
-	(No symbol) [0x0x7ff6cdaa02fa]
-	(No symbol) [0x0x7ff6cdaf7cd7]
-	(No symbol) [0x0x7ff6cdaf7f9c]
-	(No symbol) [0x0x7ff6cdb4ba87]
-	(No symbol) [0x0x7ff6cdb203bf]
-	(No symbol) [0x0x7ff6cdb487fb]
-	(No symbol) [0x0x7ff6cdb20153]
-	(No symbol) [0x0x7ff6cdae8b02]
-	(No symbol) [0x0x7ff6cdae98d3]
-	GetHandleVerifier [0x0x7ff6cdfde83d+2949837]
-	GetHandleVerifier [0x0x7ff6cdfd8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6cdff86c7+3055959]
-	GetHandleVerifier [0x0x7ff6cdd3cfee+191102]
-	GetHandleVerifier [0x0x7ff6cdd450af+224063]
-	GetHandleVerifier [0x0x7ff6cdd2af64+117236]
-	GetHandleVerifier [0x0x7ff6cdd2b119+117673]
-	GetHandleVerifier [0x0x7ff6cdd110a8+11064]
+	GetHandleVerifier [0x0x7ff7bf181eb5+80197]
+	GetHandleVerifier [0x0x7ff7bf181f10+80288]
+	(No symbol) [0x0x7ff7bef002fa]
+	(No symbol) [0x0x7ff7bef57cd7]
+	(No symbol) [0x0x7ff7bef57f9c]
+	(No symbol) [0x0x7ff7befaba87]
+	(No symbol) [0x0x7ff7bef803bf]
+	(No symbol) [0x0x7ff7befa87fb]
+	(No symbol) [0x0x7ff7bef80153]
+	(No symbol) [0x0x7ff7bef48b02]
+	(No symbol) [0x0x7ff7bef498d3]
+	GetHandleVerifier [0x0x7ff7bf43e83d+2949837]
+	GetHandleVerifier [0x0x7ff7bf438c6a+2926330]
+	GetHandleVerifier [0x0x7ff7bf4586c7+3055959]
+	GetHandleVerifier [0x0x7ff7bf19cfee+191102]
+	GetHandleVerifier [0x0x7ff7bf1a50af+224063]
+	GetHandleVerifier [0x0x7ff7bf18af64+117236]
+	GetHandleVerifier [0x0x7ff7bf18b119+117673]
+	GetHandleVerifier [0x0x7ff7bf1710a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.mgnbm.co.uk/80mm-pir-insulation-board-2400mm-x-1200mm-8-x-4/</t>
+          <t>£44.00</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£26.70</t>
+          <t>£25.99</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£26.70</t>
+          <t>£25.99</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£26.70</t>
+          <t>£25.99</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1343,27 +1343,27 @@
       <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6cdd21eb5+80197]
-	GetHandleVerifier [0x0x7ff6cdd21f10+80288]
-	(No symbol) [0x0x7ff6cdaa02fa]
-	(No symbol) [0x0x7ff6cdaf7cd7]
-	(No symbol) [0x0x7ff6cdaf7f9c]
-	(No symbol) [0x0x7ff6cdb4ba87]
-	(No symbol) [0x0x7ff6cdb203bf]
-	(No symbol) [0x0x7ff6cdb487fb]
-	(No symbol) [0x0x7ff6cdb20153]
-	(No symbol) [0x0x7ff6cdae8b02]
-	(No symbol) [0x0x7ff6cdae98d3]
-	GetHandleVerifier [0x0x7ff6cdfde83d+2949837]
-	GetHandleVerifier [0x0x7ff6cdfd8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6cdff86c7+3055959]
-	GetHandleVerifier [0x0x7ff6cdd3cfee+191102]
-	GetHandleVerifier [0x0x7ff6cdd450af+224063]
-	GetHandleVerifier [0x0x7ff6cdd2af64+117236]
-	GetHandleVerifier [0x0x7ff6cdd2b119+117673]
-	GetHandleVerifier [0x0x7ff6cdd110a8+11064]
+	GetHandleVerifier [0x0x7ff7bf181eb5+80197]
+	GetHandleVerifier [0x0x7ff7bf181f10+80288]
+	(No symbol) [0x0x7ff7bef002fa]
+	(No symbol) [0x0x7ff7bef57cd7]
+	(No symbol) [0x0x7ff7bef57f9c]
+	(No symbol) [0x0x7ff7befaba87]
+	(No symbol) [0x0x7ff7bef803bf]
+	(No symbol) [0x0x7ff7befa87fb]
+	(No symbol) [0x0x7ff7bef80153]
+	(No symbol) [0x0x7ff7bef48b02]
+	(No symbol) [0x0x7ff7bef498d3]
+	GetHandleVerifier [0x0x7ff7bf43e83d+2949837]
+	GetHandleVerifier [0x0x7ff7bf438c6a+2926330]
+	GetHandleVerifier [0x0x7ff7bf4586c7+3055959]
+	GetHandleVerifier [0x0x7ff7bf19cfee+191102]
+	GetHandleVerifier [0x0x7ff7bf1a50af+224063]
+	GetHandleVerifier [0x0x7ff7bf18af64+117236]
+	GetHandleVerifier [0x0x7ff7bf18b119+117673]
+	GetHandleVerifier [0x0x7ff7bf1710a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.mgnbm.co.uk/90mm-pir-insulation-board-2400mm-x-1200mm-8-x-4/</t>
+          <t>£39.24</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£26.40</t>
+          <t>£25.90</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£26.40</t>
+          <t>£25.90</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£26.40</t>
+          <t>£25.90</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1444,27 +1444,27 @@
       <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6cdd21eb5+80197]
-	GetHandleVerifier [0x0x7ff6cdd21f10+80288]
-	(No symbol) [0x0x7ff6cdaa02fa]
-	(No symbol) [0x0x7ff6cdaf7cd7]
-	(No symbol) [0x0x7ff6cdaf7f9c]
-	(No symbol) [0x0x7ff6cdb4ba87]
-	(No symbol) [0x0x7ff6cdb203bf]
-	(No symbol) [0x0x7ff6cdb487fb]
-	(No symbol) [0x0x7ff6cdb20153]
-	(No symbol) [0x0x7ff6cdae8b02]
-	(No symbol) [0x0x7ff6cdae98d3]
-	GetHandleVerifier [0x0x7ff6cdfde83d+2949837]
-	GetHandleVerifier [0x0x7ff6cdfd8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6cdff86c7+3055959]
-	GetHandleVerifier [0x0x7ff6cdd3cfee+191102]
-	GetHandleVerifier [0x0x7ff6cdd450af+224063]
-	GetHandleVerifier [0x0x7ff6cdd2af64+117236]
-	GetHandleVerifier [0x0x7ff6cdd2b119+117673]
-	GetHandleVerifier [0x0x7ff6cdd110a8+11064]
+	GetHandleVerifier [0x0x7ff7bf181eb5+80197]
+	GetHandleVerifier [0x0x7ff7bf181f10+80288]
+	(No symbol) [0x0x7ff7bef002fa]
+	(No symbol) [0x0x7ff7bef57cd7]
+	(No symbol) [0x0x7ff7bef57f9c]
+	(No symbol) [0x0x7ff7befaba87]
+	(No symbol) [0x0x7ff7bef803bf]
+	(No symbol) [0x0x7ff7befa87fb]
+	(No symbol) [0x0x7ff7bef80153]
+	(No symbol) [0x0x7ff7bef48b02]
+	(No symbol) [0x0x7ff7bef498d3]
+	GetHandleVerifier [0x0x7ff7bf43e83d+2949837]
+	GetHandleVerifier [0x0x7ff7bf438c6a+2926330]
+	GetHandleVerifier [0x0x7ff7bf4586c7+3055959]
+	GetHandleVerifier [0x0x7ff7bf19cfee+191102]
+	GetHandleVerifier [0x0x7ff7bf1a50af+224063]
+	GetHandleVerifier [0x0x7ff7bf18af64+117236]
+	GetHandleVerifier [0x0x7ff7bf18b119+117673]
+	GetHandleVerifier [0x0x7ff7bf1710a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.mgnbm.co.uk/100mm-pir-insulation-board-2400mm-x-1200mm-8-x-4/</t>
+          <t>£31.30</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1545,27 +1545,27 @@
       <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6cdd21eb5+80197]
-	GetHandleVerifier [0x0x7ff6cdd21f10+80288]
-	(No symbol) [0x0x7ff6cdaa02fa]
-	(No symbol) [0x0x7ff6cdaf7cd7]
-	(No symbol) [0x0x7ff6cdaf7f9c]
-	(No symbol) [0x0x7ff6cdb4ba87]
-	(No symbol) [0x0x7ff6cdb203bf]
-	(No symbol) [0x0x7ff6cdb487fb]
-	(No symbol) [0x0x7ff6cdb20153]
-	(No symbol) [0x0x7ff6cdae8b02]
-	(No symbol) [0x0x7ff6cdae98d3]
-	GetHandleVerifier [0x0x7ff6cdfde83d+2949837]
-	GetHandleVerifier [0x0x7ff6cdfd8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6cdff86c7+3055959]
-	GetHandleVerifier [0x0x7ff6cdd3cfee+191102]
-	GetHandleVerifier [0x0x7ff6cdd450af+224063]
-	GetHandleVerifier [0x0x7ff6cdd2af64+117236]
-	GetHandleVerifier [0x0x7ff6cdd2b119+117673]
-	GetHandleVerifier [0x0x7ff6cdd110a8+11064]
+	GetHandleVerifier [0x0x7ff7bf181eb5+80197]
+	GetHandleVerifier [0x0x7ff7bf181f10+80288]
+	(No symbol) [0x0x7ff7bef002fa]
+	(No symbol) [0x0x7ff7bef57cd7]
+	(No symbol) [0x0x7ff7bef57f9c]
+	(No symbol) [0x0x7ff7befaba87]
+	(No symbol) [0x0x7ff7bef803bf]
+	(No symbol) [0x0x7ff7befa87fb]
+	(No symbol) [0x0x7ff7bef80153]
+	(No symbol) [0x0x7ff7bef48b02]
+	(No symbol) [0x0x7ff7bef498d3]
+	GetHandleVerifier [0x0x7ff7bf43e83d+2949837]
+	GetHandleVerifier [0x0x7ff7bf438c6a+2926330]
+	GetHandleVerifier [0x0x7ff7bf4586c7+3055959]
+	GetHandleVerifier [0x0x7ff7bf19cfee+191102]
+	GetHandleVerifier [0x0x7ff7bf1a50af+224063]
+	GetHandleVerifier [0x0x7ff7bf18af64+117236]
+	GetHandleVerifier [0x0x7ff7bf18b119+117673]
+	GetHandleVerifier [0x0x7ff7bf1710a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.mgnbm.co.uk/110mm-pir-insulation-board-2400mm-x-1200mm-8-x-4/</t>
+          <t>£54.72</t>
         </is>
       </c>
     </row>
@@ -1605,17 +1605,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£32.25</t>
+          <t>£31.40</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£32.25</t>
+          <t>£31.40</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£32.25</t>
+          <t>£31.40</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1646,27 +1646,27 @@
       <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6cdd21eb5+80197]
-	GetHandleVerifier [0x0x7ff6cdd21f10+80288]
-	(No symbol) [0x0x7ff6cdaa02fa]
-	(No symbol) [0x0x7ff6cdaf7cd7]
-	(No symbol) [0x0x7ff6cdaf7f9c]
-	(No symbol) [0x0x7ff6cdb4ba87]
-	(No symbol) [0x0x7ff6cdb203bf]
-	(No symbol) [0x0x7ff6cdb487fb]
-	(No symbol) [0x0x7ff6cdb20153]
-	(No symbol) [0x0x7ff6cdae8b02]
-	(No symbol) [0x0x7ff6cdae98d3]
-	GetHandleVerifier [0x0x7ff6cdfde83d+2949837]
-	GetHandleVerifier [0x0x7ff6cdfd8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6cdff86c7+3055959]
-	GetHandleVerifier [0x0x7ff6cdd3cfee+191102]
-	GetHandleVerifier [0x0x7ff6cdd450af+224063]
-	GetHandleVerifier [0x0x7ff6cdd2af64+117236]
-	GetHandleVerifier [0x0x7ff6cdd2b119+117673]
-	GetHandleVerifier [0x0x7ff6cdd110a8+11064]
+	GetHandleVerifier [0x0x7ff7bf181eb5+80197]
+	GetHandleVerifier [0x0x7ff7bf181f10+80288]
+	(No symbol) [0x0x7ff7bef002fa]
+	(No symbol) [0x0x7ff7bef57cd7]
+	(No symbol) [0x0x7ff7bef57f9c]
+	(No symbol) [0x0x7ff7befaba87]
+	(No symbol) [0x0x7ff7bef803bf]
+	(No symbol) [0x0x7ff7befa87fb]
+	(No symbol) [0x0x7ff7bef80153]
+	(No symbol) [0x0x7ff7bef48b02]
+	(No symbol) [0x0x7ff7bef498d3]
+	GetHandleVerifier [0x0x7ff7bf43e83d+2949837]
+	GetHandleVerifier [0x0x7ff7bf438c6a+2926330]
+	GetHandleVerifier [0x0x7ff7bf4586c7+3055959]
+	GetHandleVerifier [0x0x7ff7bf19cfee+191102]
+	GetHandleVerifier [0x0x7ff7bf1a50af+224063]
+	GetHandleVerifier [0x0x7ff7bf18af64+117236]
+	GetHandleVerifier [0x0x7ff7bf18b119+117673]
+	GetHandleVerifier [0x0x7ff7bf1710a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.mgnbm.co.uk/120mm-pir-insulation-board-2400mm-x-1200mm-8-x-4/</t>
+          <t>£39.99</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1824,27 +1824,27 @@
       <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6cdd21eb5+80197]
-	GetHandleVerifier [0x0x7ff6cdd21f10+80288]
-	(No symbol) [0x0x7ff6cdaa02fa]
-	(No symbol) [0x0x7ff6cdaf7cd7]
-	(No symbol) [0x0x7ff6cdaf7f9c]
-	(No symbol) [0x0x7ff6cdb4ba87]
-	(No symbol) [0x0x7ff6cdb203bf]
-	(No symbol) [0x0x7ff6cdb487fb]
-	(No symbol) [0x0x7ff6cdb20153]
-	(No symbol) [0x0x7ff6cdae8b02]
-	(No symbol) [0x0x7ff6cdae98d3]
-	GetHandleVerifier [0x0x7ff6cdfde83d+2949837]
-	GetHandleVerifier [0x0x7ff6cdfd8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6cdff86c7+3055959]
-	GetHandleVerifier [0x0x7ff6cdd3cfee+191102]
-	GetHandleVerifier [0x0x7ff6cdd450af+224063]
-	GetHandleVerifier [0x0x7ff6cdd2af64+117236]
-	GetHandleVerifier [0x0x7ff6cdd2b119+117673]
-	GetHandleVerifier [0x0x7ff6cdd110a8+11064]
+	GetHandleVerifier [0x0x7ff7bf181eb5+80197]
+	GetHandleVerifier [0x0x7ff7bf181f10+80288]
+	(No symbol) [0x0x7ff7bef002fa]
+	(No symbol) [0x0x7ff7bef57cd7]
+	(No symbol) [0x0x7ff7bef57f9c]
+	(No symbol) [0x0x7ff7befaba87]
+	(No symbol) [0x0x7ff7bef803bf]
+	(No symbol) [0x0x7ff7befa87fb]
+	(No symbol) [0x0x7ff7bef80153]
+	(No symbol) [0x0x7ff7bef48b02]
+	(No symbol) [0x0x7ff7bef498d3]
+	GetHandleVerifier [0x0x7ff7bf43e83d+2949837]
+	GetHandleVerifier [0x0x7ff7bf438c6a+2926330]
+	GetHandleVerifier [0x0x7ff7bf4586c7+3055959]
+	GetHandleVerifier [0x0x7ff7bf19cfee+191102]
+	GetHandleVerifier [0x0x7ff7bf1a50af+224063]
+	GetHandleVerifier [0x0x7ff7bf18af64+117236]
+	GetHandleVerifier [0x0x7ff7bf18b119+117673]
+	GetHandleVerifier [0x0x7ff7bf1710a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.mgnbm.co.uk/130mm-pir-insulation-board-2400mm-x-1200mm-8-x-4/</t>
+          <t>£63.12</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1925,27 +1925,27 @@
       <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6cdd21eb5+80197]
-	GetHandleVerifier [0x0x7ff6cdd21f10+80288]
-	(No symbol) [0x0x7ff6cdaa02fa]
-	(No symbol) [0x0x7ff6cdaf7cd7]
-	(No symbol) [0x0x7ff6cdaf7f9c]
-	(No symbol) [0x0x7ff6cdb4ba87]
-	(No symbol) [0x0x7ff6cdb203bf]
-	(No symbol) [0x0x7ff6cdb487fb]
-	(No symbol) [0x0x7ff6cdb20153]
-	(No symbol) [0x0x7ff6cdae8b02]
-	(No symbol) [0x0x7ff6cdae98d3]
-	GetHandleVerifier [0x0x7ff6cdfde83d+2949837]
-	GetHandleVerifier [0x0x7ff6cdfd8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6cdff86c7+3055959]
-	GetHandleVerifier [0x0x7ff6cdd3cfee+191102]
-	GetHandleVerifier [0x0x7ff6cdd450af+224063]
-	GetHandleVerifier [0x0x7ff6cdd2af64+117236]
-	GetHandleVerifier [0x0x7ff6cdd2b119+117673]
-	GetHandleVerifier [0x0x7ff6cdd110a8+11064]
+	GetHandleVerifier [0x0x7ff7bf181eb5+80197]
+	GetHandleVerifier [0x0x7ff7bf181f10+80288]
+	(No symbol) [0x0x7ff7bef002fa]
+	(No symbol) [0x0x7ff7bef57cd7]
+	(No symbol) [0x0x7ff7bef57f9c]
+	(No symbol) [0x0x7ff7befaba87]
+	(No symbol) [0x0x7ff7bef803bf]
+	(No symbol) [0x0x7ff7befa87fb]
+	(No symbol) [0x0x7ff7bef80153]
+	(No symbol) [0x0x7ff7bef48b02]
+	(No symbol) [0x0x7ff7bef498d3]
+	GetHandleVerifier [0x0x7ff7bf43e83d+2949837]
+	GetHandleVerifier [0x0x7ff7bf438c6a+2926330]
+	GetHandleVerifier [0x0x7ff7bf4586c7+3055959]
+	GetHandleVerifier [0x0x7ff7bf19cfee+191102]
+	GetHandleVerifier [0x0x7ff7bf1a50af+224063]
+	GetHandleVerifier [0x0x7ff7bf18af64+117236]
+	GetHandleVerifier [0x0x7ff7bf18b119+117673]
+	GetHandleVerifier [0x0x7ff7bf1710a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.mgnbm.co.uk/140mm-pir-insulation-board-2400mm-x-1200mm-8-x-4/</t>
+          <t>£66.31</t>
         </is>
       </c>
     </row>
@@ -1985,17 +1985,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£39.99</t>
+          <t>£38.30</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>£39.99</t>
+          <t>£38.30</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>£39.99</t>
+          <t>£38.30</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2026,27 +2026,27 @@
       <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6cdd21eb5+80197]
-	GetHandleVerifier [0x0x7ff6cdd21f10+80288]
-	(No symbol) [0x0x7ff6cdaa02fa]
-	(No symbol) [0x0x7ff6cdaf7cd7]
-	(No symbol) [0x0x7ff6cdaf7f9c]
-	(No symbol) [0x0x7ff6cdb4ba87]
-	(No symbol) [0x0x7ff6cdb203bf]
-	(No symbol) [0x0x7ff6cdb487fb]
-	(No symbol) [0x0x7ff6cdb20153]
-	(No symbol) [0x0x7ff6cdae8b02]
-	(No symbol) [0x0x7ff6cdae98d3]
-	GetHandleVerifier [0x0x7ff6cdfde83d+2949837]
-	GetHandleVerifier [0x0x7ff6cdfd8c6a+2926330]
-	GetHandleVerifier [0x0x7ff6cdff86c7+3055959]
-	GetHandleVerifier [0x0x7ff6cdd3cfee+191102]
-	GetHandleVerifier [0x0x7ff6cdd450af+224063]
-	GetHandleVerifier [0x0x7ff6cdd2af64+117236]
-	GetHandleVerifier [0x0x7ff6cdd2b119+117673]
-	GetHandleVerifier [0x0x7ff6cdd110a8+11064]
+	GetHandleVerifier [0x0x7ff7bf181eb5+80197]
+	GetHandleVerifier [0x0x7ff7bf181f10+80288]
+	(No symbol) [0x0x7ff7bef002fa]
+	(No symbol) [0x0x7ff7bef57cd7]
+	(No symbol) [0x0x7ff7bef57f9c]
+	(No symbol) [0x0x7ff7befaba87]
+	(No symbol) [0x0x7ff7bef803bf]
+	(No symbol) [0x0x7ff7befa87fb]
+	(No symbol) [0x0x7ff7bef80153]
+	(No symbol) [0x0x7ff7bef48b02]
+	(No symbol) [0x0x7ff7bef498d3]
+	GetHandleVerifier [0x0x7ff7bf43e83d+2949837]
+	GetHandleVerifier [0x0x7ff7bf438c6a+2926330]
+	GetHandleVerifier [0x0x7ff7bf4586c7+3055959]
+	GetHandleVerifier [0x0x7ff7bf19cfee+191102]
+	GetHandleVerifier [0x0x7ff7bf1a50af+224063]
+	GetHandleVerifier [0x0x7ff7bf18af64+117236]
+	GetHandleVerifier [0x0x7ff7bf18b119+117673]
+	GetHandleVerifier [0x0x7ff7bf1710a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.mgnbm.co.uk/150mm-pir-insulation-board-2400mm-x-1200mm-8-x-4/</t>
+          <t>£53.91</t>
         </is>
       </c>
     </row>
